--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -555,157 +555,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daviddesco1</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,142 +451,142 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F2" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>86</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -595,24 +595,24 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>86</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -647,65 +647,65 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
         <v>97</v>
       </c>
       <c r="F9" t="n">
-        <v>86</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,90 +451,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,50 +543,50 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -595,91 +595,91 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,76 +465,76 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>PacoSarra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Ibra</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,50 +543,50 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E6" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -595,91 +595,91 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>PavelMel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Mélissa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         <v>23</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,64 +451,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Ppo28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Prescylla</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -517,24 +517,24 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PacoSarra</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ibra</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,169 +543,169 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PavelMel</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mélissa</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,64 +451,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ppo28</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prescylla</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -517,50 +517,50 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72</v>
+      </c>
+      <c r="F5" t="n">
         <v>27</v>
-      </c>
-      <c r="E5" t="n">
-        <v>46</v>
-      </c>
-      <c r="F5" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -569,24 +569,24 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -595,24 +595,24 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,91 +621,91 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -529,38 +529,38 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -569,50 +569,50 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Laetice2020</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Laetitia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,36 +621,36 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="E8" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
@@ -659,24 +659,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
         <v>22</v>
@@ -685,27 +685,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Julie_Romao</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,116 +451,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Francisco93</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -569,50 +565,50 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
+        <v>96</v>
+      </c>
+      <c r="F7" t="n">
         <v>30</v>
-      </c>
-      <c r="F7" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Laetice2020</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Laetitia</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,50 +617,50 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -673,35 +669,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Julie</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
       <c r="D11" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -468,10 +468,10 @@
         <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -490,10 +490,10 @@
         <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -516,10 +516,10 @@
         <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -542,10 +542,10 @@
         <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -568,59 +568,59 @@
         <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E8" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
         <v>30</v>
@@ -629,12 +629,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F9" t="n">
         <v>30</v>
@@ -655,24 +655,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>WIL1610</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
         <v>29</v>
@@ -681,27 +681,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Kaliced</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Kalice</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,60 +451,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Francisco93</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>François</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Camille</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -513,50 +517,50 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -565,24 +569,24 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>23</v>
+      </c>
+      <c r="E6" t="n">
         <v>44</v>
       </c>
-      <c r="E6" t="n">
-        <v>77</v>
-      </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>lenaaik</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Lénaïk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -594,47 +598,47 @@
         <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Selver</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -643,65 +647,65 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kaliced</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kalice</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,64 +451,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -517,128 +517,128 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lenaaik</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lénaïk</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -647,65 +647,65 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,38 +451,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>1993ahm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lilia</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="E2" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -491,128 +487,128 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,91 +617,91 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,124 +451,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1993ahm</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ahmed</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t xml:space="preserve">Oswaina </t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>compta</t>
+        </is>
+      </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Julie_Romao</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>christophe</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>24</v>
@@ -577,131 +577,131 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E11" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,38 +451,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -491,24 +491,24 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
@@ -529,86 +529,90 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Julie</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Ambre</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -617,76 +621,76 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -695,13 +699,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,168 +451,164 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>goat#AD6GS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Candice</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E7" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Droit_au_but7723</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Calixthe</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,24 +617,24 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -647,65 +643,65 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cleem22</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clemence</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,257 +451,257 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>goat</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Gabrielle</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
       <c r="D2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Lison</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>goat#AD6GS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Damien</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E9" t="n">
         <v>87</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,128 +451,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Francisco93</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Romain J</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mylene-Jnt</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mylène</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
         <v>12</v>
@@ -581,24 +577,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>goat#AD6GS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lison</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>goat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E7" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
@@ -607,24 +599,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F8" t="n">
         <v>11</v>
@@ -633,46 +625,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>goat</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
@@ -681,27 +677,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,86 +451,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Francisco93</t>
+          <t>Seesee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>François</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>GLR_PRIME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Liliuus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Lilia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -539,165 +543,169 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>C4M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>goat#AD6GS</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>goat</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Gronaldo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
       <c r="D7" t="n">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,53 +451,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>Julie_Romao</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Selver</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -517,50 +513,50 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Liliuus</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lilia</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C4M</t>
+          <t>JeremFZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Jérémy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -569,143 +565,143 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>MatuRenard</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Mathias</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Ambrepic</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Ambre</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E10" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,60 +451,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Chadia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Julie</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Yassine Z</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GLR_PRIME</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -513,65 +517,65 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JeremFZ</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jérémy</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="E6" t="n">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -591,102 +595,102 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ambrepic</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ambre</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Ninaaaa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>GOAT#UE2WM8M9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Marilena</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -695,13 +699,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,168 +451,168 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Soraya-Y</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Soraya</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>31</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MatuRenard</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mathias</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>LilianeB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t xml:space="preserve">Liliane </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -621,36 +621,36 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Erwan#4G91X</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Erwan</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
@@ -659,12 +659,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ninaaaa</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -673,24 +673,24 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOAT#UE2WM8M9</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marilena</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,194 +451,194 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Elisewiss</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Soraya-Y</t>
+          <t>PANENKANY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Soraya</t>
+          <t>Damien</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LilianeB</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liliane </t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -647,50 +647,50 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -468,10 +468,10 @@
         <v>51</v>
       </c>
       <c r="E2" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -494,36 +494,36 @@
         <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -546,59 +546,59 @@
         <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>YassineZ95</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Yassine Z</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
@@ -607,50 +607,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="E8" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -659,38 +659,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,128 +465,124 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Julie_Romao</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tedy</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PANENKANY</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Damien</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>YassineZ95</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yassine Z</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -595,102 +591,98 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>Fa_One</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paula</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -699,13 +691,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,86 +451,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Julie</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -539,24 +543,24 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E5" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -565,84 +569,88 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>chaychaychay</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Chaymaa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fa_One</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Farah</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
@@ -651,24 +659,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
         <v>7</v>
@@ -677,12 +685,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Gronaldo_95</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Gronaldo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -691,10 +699,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
         <v>7</v>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,24 +451,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" t="n">
         <v>16</v>
@@ -477,24 +477,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
@@ -520,10 +520,10 @@
         <v>56</v>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -546,10 +546,10 @@
         <v>36</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -572,10 +572,10 @@
         <v>37</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -598,114 +598,114 @@
         <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Mr-Worldwide</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gronaldo_95</t>
+          <t>A-MOE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gronaldo</t>
+          <t>Françoise</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,64 +451,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>Julie_Romao</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Loïc</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -517,195 +513,191 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Francisco93</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Walid</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>chaychaychay</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chaymaa</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mr-Worldwide</t>
+          <t>Paulasipi1998</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-MOE</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Françoise</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,186 +451,190 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Julie_Romao</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Julie</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Francisco93</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>François</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>romain</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Francisco93</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brayen</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>ChrisKr1Deg1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>christophe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Timy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -639,65 +643,65 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="E11" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,38 +451,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Filipinho95</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Filipe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -491,136 +491,136 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>46</v>
+      </c>
+      <c r="E3" t="n">
         <v>53</v>
       </c>
-      <c r="E3" t="n">
-        <v>63</v>
-      </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E4" t="n">
         <v>45</v>
       </c>
-      <c r="E4" t="n">
-        <v>55</v>
-      </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Fa_One</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>romain</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Farah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Francisco93</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>François</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Walid</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ChrisKr1Deg1</t>
+          <t>Emma_Noel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>christophe</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Timy</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
@@ -629,12 +629,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -643,62 +643,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Francisco93</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
+          <t>François</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>EmyEnzo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,112 +451,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Filipinho95</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Filipe</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>GOAT#UE4U8KA6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Jean Baptiste</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E4" t="n">
         <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fa_One</t>
+          <t>Taylor2901</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>ousmane</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -565,139 +565,143 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Emma_Noel</t>
+          <t>Exia95</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Loïc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stephbreton</t>
+          <t>Fuzo697</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STEPHANE</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Valentine___</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Francisco93</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>François</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Hamza</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Teddbear</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Tedy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,124 +465,128 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GOAT#UE4U8KA6</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jean Baptiste</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Taylor2901</t>
+          <t>Lyzone</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ousmane</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Lison</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
       <c r="D5" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>Priscilla#4LCAF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Priscilla</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Exia95</t>
+          <t>MT35T</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Loïc</t>
+          <t>Mathilde</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -591,24 +595,24 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fuzo697</t>
+          <t>Marie__92</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Marie</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -617,91 +621,91 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Valentine___</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Valentine</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Rosa_1009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Rosaline</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Teddbear</t>
+          <t>Pipou931</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tedy</t>
+          <t>Juliie</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,261 +451,261 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Leandrocp</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Leandro</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lyzone</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lison</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Priscilla#4LCAF</t>
+          <t>Cindie_JJA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Priscilla</t>
+          <t>Cindie</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MT35T</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mathilde</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E7" t="n">
         <v>26</v>
       </c>
-      <c r="E7" t="n">
-        <v>32</v>
-      </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marie__92</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Marie</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ceciledp</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cécile</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pipou931</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Juliie</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,90 +451,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Leandrocp</t>
+          <t>RomainLect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Leandro</t>
+          <t>romain</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Emilay</t>
+          <t>Melissagzb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Émilie</t>
+          <t>Melissa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,36 +543,36 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cindie_JJA</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cindie</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -581,24 +581,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>BrickXVI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ouissal</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -607,105 +603,105 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AudreyB225</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audrey</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FRHTCTD10</t>
+          <t>dian-bgt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Candice</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E10" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Camillewbl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,76 +451,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>Fethinho</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Fethi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RomainLect</t>
+          <t>Ouiouiausoleil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>romain</t>
+          <t>Ouissal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Melissagzb</t>
+          <t>WalidSiuuuuu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melissa</t>
+          <t>Walid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -529,112 +529,116 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coucoucassecou</t>
+          <t>Maruyama</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brayen</t>
+          <t>Gabrielle</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>BadrLeo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Badr Leo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
+          <t>Chadia__</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brick</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>Chadia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>HamzaG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Ze_GOAT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Yasser</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -643,24 +647,24 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dian-bgt</t>
+          <t>abihuts</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Antonio Moctezuma</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -669,36 +673,36 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Camillewbl</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,64 +451,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>BrickXVI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fethi</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ouiouiausoleil</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ouissal</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WalidSiuuuuu</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Walid</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -517,10 +513,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -529,24 +525,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Maruyama</t>
+          <t>SamSamH8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gabrielle</t>
+          <t>Samia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -555,24 +551,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BadrLeo</t>
+          <t>Krol#4R8XC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Badr Leo</t>
+          <t>Krol</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -581,24 +577,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chadia__</t>
+          <t>Matt#4B4CU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chadia</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -607,38 +603,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HamzaG</t>
+          <t>Anais757817</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Anaïs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ze_GOAT</t>
+          <t>BOUGA#2JGXP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yasser</t>
+          <t>BOUGA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -647,10 +643,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -659,12 +655,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>abihuts</t>
+          <t>Camss</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Antonio Moctezuma</t>
+          <t>Camille</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -673,10 +669,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -685,12 +681,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Yebri</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Brieuc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -699,13 +695,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,60 +451,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brick</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Romain J</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>DJOSWA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t xml:space="preserve">Oswaina </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Davido#4BZ54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>Davido</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -513,154 +517,154 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SamSamH8</t>
+          <t>RBTL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samia</t>
+          <t>lea</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Krol#4R8XC</t>
+          <t>Kolas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Krol</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Matt#4B4CU</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Anais757817</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Anaïs</t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BOUGA#2JGXP</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BOUGA</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Camss</t>
+          <t>JKInternational</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Camille</t>
+          <t>Joachim</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -669,39 +673,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yebri</t>
+          <t>MargauxCtln</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Brieuc</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,90 +451,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Romain_JO</t>
+          <t>Emilay</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Romain J</t>
+          <t>Émilie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DJOSWA</t>
+          <t>SID-F-ANDRE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oswaina </t>
+          <t>Denis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>compta</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Davido#4BZ54</t>
+          <t>FRHTCTD10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Davido</t>
+          <t>Candice</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RBTL</t>
+          <t>Mylene-Jnt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lea</t>
+          <t>Mylène</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,102 +543,102 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kolas</t>
+          <t>davidd23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nonito20</t>
+          <t>Devilrock95</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arnaud</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SID-F-ANDRE</t>
+          <t>Marion1822</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Denis</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ilan_260_</t>
+          <t>Nonito20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ilann </t>
+          <t>Arnaud</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -647,65 +647,65 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JKInternational</t>
+          <t>Stephbreton</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Joachim</t>
+          <t>STEPHANE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MargauxCtln</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Margaux</t>
+          <t>Clemence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>commerce</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,266 +446,6 @@
         <is>
           <t>Chute</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Emilay</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Émilie</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SID-F-ANDRE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Denis</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Reste du monde</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>17</v>
-      </c>
-      <c r="E3" t="n">
-        <v>19</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FRHTCTD10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Candice</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>69</v>
-      </c>
-      <c r="E4" t="n">
-        <v>71</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mylene-Jnt</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mylène</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>offre</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>68</v>
-      </c>
-      <c r="E5" t="n">
-        <v>70</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>davidd23</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" t="n">
-        <v>13</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Devilrock95</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Steve</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>opération</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Marion1822</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Marion</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E8" t="n">
-        <v>16</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Nonito20</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Arnaud</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>19</v>
-      </c>
-      <c r="E9" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Stephbreton</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>STEPHANE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>compta</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>21</v>
-      </c>
-      <c r="E10" t="n">
-        <v>22</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cleem22</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Clemence</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>commerce</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>22</v>
-      </c>
-      <c r="E11" t="n">
-        <v>23</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,6 +448,262 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BrickXVI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Fethinho</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fethi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EmyEnzo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>offre</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>39</v>
+      </c>
+      <c r="E4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WIL1610</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>38</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Devilrock95</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>davidd23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Paulasipi1998</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Paula</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>34</v>
+      </c>
+      <c r="E8" t="n">
+        <v>37</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rosa_1009</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rosaline</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MyriamAmr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Reste du monde</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E10" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Seesee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Selver</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>opération</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>75</v>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/chutes.xlsx
+++ b/chutes.xlsx
@@ -451,138 +451,142 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BrickXVI</t>
+          <t>Cleem22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Brick</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Clemence</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>commerce</t>
+        </is>
+      </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fethinho</t>
+          <t>Coucoucassecou</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fethi</t>
+          <t>Brayen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>offre</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EmyEnzo</t>
+          <t>Romain_JO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Romain J</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>offre</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WIL1610</t>
+          <t>Erwan#4G91X</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Erwan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devilrock95</t>
+          <t>Elisewiss</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>davidd23</t>
+          <t>Ceciledp</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Cécile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -591,50 +595,50 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paulasipi1998</t>
+          <t>MyriamAmr</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Myriam</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>commerce</t>
+          <t>Reste du monde</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>34</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rosa_1009</t>
+          <t>Ilan_260_</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rosaline</t>
+          <t xml:space="preserve">Ilann </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -643,65 +647,65 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MyriamAmr</t>
+          <t>Droit_au_but7723</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Myriam</t>
+          <t>Calixthe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reste du monde</t>
+          <t>opération</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Seesee</t>
+          <t>AudreyB225</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Selver</t>
+          <t>Audrey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>opération</t>
+          <t>compta</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
